--- a/Testing sheet.xlsx
+++ b/Testing sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2f89ac1554dddab/1. TILM/Localisation/2025 Fall/Software I18n and L10n/20251201001 Testing 2/01-Source code/TRLM8620-Final-GroupA1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{A198C8A2-A6BA-4144-9BD2-EBB530BF628E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1076964B-27C3-42B9-B590-36BD5987232A}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{A198C8A2-A6BA-4144-9BD2-EBB530BF628E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E69AC4BE-14AB-4BD1-8300-2D6F98DF52FC}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E63CAE24-2F72-420F-AB06-77A71E11E222}"/>
   </bookViews>
@@ -103,15 +103,160 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>我们提供您应对银河系</t>
-    </r>
+      <t>载具</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>卡片姓名</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>确认下单</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处理中</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC-01</t>
+  </si>
+  <si>
+    <t>Homepage Loads Correctly</t>
+  </si>
+  <si>
+    <t>TC-02</t>
+  </si>
+  <si>
+    <t>Product Listing Page</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>Product Detail Page</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>Add to Cart</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>Checkout – Language Display</t>
+  </si>
+  <si>
+    <t>Homepage displays without errors; all text appears in the correct language; navigation menu, logo, and hero banner load properly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Products display with name, price, image, and localized text; no missing translation strings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Product title, description, price, and “Add to Cart” button appear correctly; images load</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clicking “Add to Cart” adds the correct product; cart count updates; user stays on the same page or receives confirmation message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Checkout pages (cart </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> shipping </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> payment) display all elements in the selected language with correct currency format; no untranslated strings</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我们提供应对银河系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
       <t>(G11n)</t>
     </r>
     <r>
@@ -127,182 +272,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>帝国币符号</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>载具</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>浏览全部载具</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>卡片姓名</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>确认下单</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>处理中</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TC-01</t>
-  </si>
-  <si>
-    <t>Homepage Loads Correctly</t>
-  </si>
-  <si>
-    <t>TC-02</t>
-  </si>
-  <si>
-    <t>Product Listing Page</t>
-  </si>
-  <si>
-    <t>TC-03</t>
-  </si>
-  <si>
-    <t>Product Detail Page</t>
-  </si>
-  <si>
-    <t>TC-04</t>
-  </si>
-  <si>
-    <t>Add to Cart</t>
-  </si>
-  <si>
-    <t>TC-05</t>
-  </si>
-  <si>
-    <t>Checkout – Language Display</t>
-  </si>
-  <si>
-    <t>Homepage displays without errors; all text appears in the correct language; navigation menu, logo, and hero banner load properly</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Products display with name, price, image, and localized text; no missing translation strings</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Product title, description, price, and “Add to Cart” button appear correctly; images load</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clicking “Add to Cart” adds the correct product; cart count updates; user stays on the same page or receives confirmation message</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Checkout pages (cart </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> shipping </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> payment) display all elements in the selected language with correct currency format; no untranslated strings</t>
-    </r>
+    <t>帝国信用币符号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浏览载具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +349,13 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -403,7 +392,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -419,9 +408,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -433,6 +419,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,6 +441,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -771,98 +767,98 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.9296875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="28.19921875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="32.06640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.9296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.19921875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="32.06640625" style="5" customWidth="1"/>
     <col min="4" max="4" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="63" x14ac:dyDescent="0.4">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
+        <v>54</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="6">
-        <v>49</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>56</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
+        <v>72</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="6">
-        <v>54</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
+        <v>82</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="6">
-        <v>56</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="5">
+        <v>101</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="6">
-        <v>72</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="6">
-        <v>82</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="6">
-        <v>101</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -898,72 +894,72 @@
     </row>
     <row r="2" spans="1:4" ht="71.25" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="57" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="57" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="71.25" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="9" t="s">
         <v>32</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="85.5" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
